--- a/Deliverables/BOM/PCBWay-BOM.xlsx
+++ b/Deliverables/BOM/PCBWay-BOM.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Iftikhar Ahmed\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\Melih-SoundSensor\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034869BD-28C7-40A8-B4A2-E4E89A920FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
     <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
+    <sheet name="10 Boards" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="245">
   <si>
     <t>Component list</t>
   </si>
@@ -80,9 +80,6 @@
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C2, C23, C26, C28, C137, C138, C139, C140</t>
-  </si>
-  <si>
     <t>C3, C5, C7, C9, C11, C13, C15, C17, C24, C25, C27, C29, C30, C32, C35, C39, C42, C53, C55, C64, C65, C66, C67, C70, C72, C76, C78, C85, C90, C91, C92, C93, C94, C95, C98, C99, C108, C112, C113, C114, C116, C118, C120, C128, C135, C136, C165, C166, C167, C168, C#2</t>
   </si>
   <si>
@@ -158,9 +155,6 @@
     <t>R11, R12</t>
   </si>
   <si>
-    <t>R15, R16, R17, R18, R19, R20, R21, R28, R29, R30, R31, R32, R33, R36, R37, R40, R41</t>
-  </si>
-  <si>
     <t>R44, R45, R46, R47</t>
   </si>
   <si>
@@ -437,9 +431,6 @@
     <t>CC0402KRX5R7BB104</t>
   </si>
   <si>
-    <t>C1608X5R1E106M080AC</t>
-  </si>
-  <si>
     <t>CC0603JRNPO9BN100</t>
   </si>
   <si>
@@ -557,9 +548,6 @@
     <t>C106204</t>
   </si>
   <si>
-    <t>C2168289</t>
-  </si>
-  <si>
     <t>C106245</t>
   </si>
   <si>
@@ -746,12 +734,6 @@
     <t>RS-03K104JT</t>
   </si>
   <si>
-    <t>TSSOP-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> MOQ (5 Boards)</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
@@ -759,12 +741,39 @@
   </si>
   <si>
     <t>Sound_Sensor</t>
+  </si>
+  <si>
+    <t>C1,C2, C23, C26, C28, C137, C138, C139, C140</t>
+  </si>
+  <si>
+    <t>C1608X5R1E106MT000E</t>
+  </si>
+  <si>
+    <t>SOD-323</t>
+  </si>
+  <si>
+    <t>R15, R16, R17,  R18, R19, R20, R21, R28, R29, R30, R31, R32, R33, R36, R37, R40, R41</t>
+  </si>
+  <si>
+    <t>30TSSOP</t>
+  </si>
+  <si>
+    <t>C76614</t>
+  </si>
+  <si>
+    <t>C62892</t>
+  </si>
+  <si>
+    <t>MOQ (5 Boards)</t>
+  </si>
+  <si>
+    <t>MOQ (10 Boards)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
@@ -908,10 +917,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <strike/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <sz val="9"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -943,7 +950,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -1203,11 +1210,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1300,9 +1320,6 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1376,26 +1393,73 @@
     <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1463,6 +1527,60 @@
         <a:xfrm>
           <a:off x="17506950" y="629542"/>
           <a:ext cx="1857375" cy="1104008"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>19942</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1905001</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12344401" y="629542"/>
+          <a:ext cx="1885950" cy="1104008"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1736,7 +1854,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1765,21 +1883,21 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
     </row>
     <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
-      <c r="C2" s="46"/>
+      <c r="C2" s="45"/>
       <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="10"/>
-      <c r="F2" s="54" t="s">
-        <v>240</v>
+      <c r="F2" s="53" t="s">
+        <v>234</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="3"/>
@@ -1787,18 +1905,18 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
-      <c r="M2" s="43"/>
+      <c r="M2" s="42"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="47"/>
+      <c r="C3" s="46"/>
       <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="55" t="s">
-        <v>241</v>
+      <c r="F3" s="54" t="s">
+        <v>235</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="4"/>
@@ -1806,18 +1924,18 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
-      <c r="M3" s="68"/>
+      <c r="M3" s="65"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="47"/>
+      <c r="C4" s="46"/>
       <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="55" t="s">
-        <v>241</v>
+      <c r="F4" s="54" t="s">
+        <v>235</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="6"/>
@@ -1825,17 +1943,17 @@
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
-      <c r="M4" s="69"/>
+      <c r="M4" s="66"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="47"/>
+      <c r="C5" s="46"/>
       <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="56" t="s">
+      <c r="F5" s="55" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="14"/>
@@ -1844,12 +1962,12 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
-      <c r="M5" s="69"/>
+      <c r="M5" s="66"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
-      <c r="C6" s="48"/>
+      <c r="C6" s="47"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
@@ -1859,12 +1977,12 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="69"/>
+      <c r="M6" s="66"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="49"/>
+      <c r="C7" s="48"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
@@ -1874,12 +1992,12 @@
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
-      <c r="M7" s="69"/>
+      <c r="M7" s="66"/>
     </row>
     <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="50"/>
+      <c r="C8" s="49"/>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
@@ -1889,1567 +2007,1566 @@
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
-      <c r="M8" s="69"/>
+      <c r="M8" s="66"/>
     </row>
     <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="67" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="D9" s="29" t="s">
+      <c r="D9" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="30" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="G9" s="30" t="s">
-        <v>126</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="I9" s="30" t="s">
-        <v>169</v>
+      <c r="E9" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>166</v>
       </c>
       <c r="J9" s="29" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="K9" s="29" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="L9" s="29" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="M9" s="31" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="53">
+      <c r="B10" s="52">
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="38" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="G10" s="38" t="s">
-        <v>127</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I10" s="39" t="s">
-        <v>170</v>
-      </c>
-      <c r="J10" s="58" t="s">
-        <v>185</v>
-      </c>
-      <c r="K10" s="39">
+      <c r="D10" s="68" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="J10" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="K10" s="38">
         <v>9</v>
       </c>
-      <c r="L10" s="39">
+      <c r="L10" s="38">
         <v>60</v>
       </c>
-      <c r="M10" s="41"/>
+      <c r="M10" s="40"/>
     </row>
     <row r="11" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="53">
-        <f t="shared" ref="B11:B49" si="0">ROW(B11) - ROW($B$9)</f>
+      <c r="B11" s="52">
+        <f>ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="H11" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="I11" s="39" t="s">
-        <v>171</v>
-      </c>
-      <c r="J11" s="58" t="s">
-        <v>186</v>
-      </c>
-      <c r="K11" s="39">
+      <c r="D11" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="J11" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K11" s="38">
         <v>51</v>
       </c>
-      <c r="L11" s="39">
+      <c r="L11" s="38">
         <v>300</v>
       </c>
-      <c r="M11" s="42"/>
+      <c r="M11" s="41"/>
     </row>
     <row r="12" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="53">
-        <f>ROW(B12) - ROW($B$9)</f>
+      <c r="B12" s="52">
+        <f t="shared" ref="B12:B48" si="0">ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="37" t="s">
-        <v>17</v>
+      <c r="D12" s="69" t="s">
+        <v>16</v>
       </c>
       <c r="E12" s="38" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I12" s="39" t="s">
-        <v>210</v>
-      </c>
-      <c r="J12" s="58" t="s">
-        <v>187</v>
-      </c>
-      <c r="K12" s="59">
+        <v>56</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="J12" s="57" t="s">
+        <v>183</v>
+      </c>
+      <c r="K12" s="58">
         <v>12</v>
       </c>
-      <c r="L12" s="39">
+      <c r="L12" s="38">
         <v>100</v>
       </c>
-      <c r="M12" s="41"/>
+      <c r="M12" s="40"/>
     </row>
     <row r="13" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="53">
-        <f t="shared" si="0"/>
+      <c r="B13" s="52">
+        <f>ROW(B13) - ROW($B$9)</f>
         <v>4</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="G13" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="H13" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="I13" s="39" t="s">
-        <v>172</v>
-      </c>
-      <c r="J13" s="58" t="s">
-        <v>188</v>
-      </c>
-      <c r="K13" s="39">
+      <c r="D13" s="68" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="I13" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="J13" s="57" t="s">
+        <v>184</v>
+      </c>
+      <c r="K13" s="38">
         <v>2</v>
       </c>
-      <c r="L13" s="39">
+      <c r="L13" s="38">
         <v>11</v>
       </c>
-      <c r="M13" s="42"/>
+      <c r="M13" s="41"/>
     </row>
     <row r="14" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
-      <c r="B14" s="53">
+      <c r="B14" s="52">
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="37" t="s">
-        <v>19</v>
+      <c r="D14" s="69" t="s">
+        <v>18</v>
       </c>
       <c r="E14" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="G14" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="H14" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I14" s="39" t="s">
-        <v>211</v>
-      </c>
-      <c r="J14" s="58" t="s">
-        <v>189</v>
-      </c>
-      <c r="K14" s="59">
+        <v>58</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="J14" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="K14" s="58">
         <v>16</v>
       </c>
-      <c r="L14" s="39">
+      <c r="L14" s="38">
         <v>100</v>
       </c>
-      <c r="M14" s="41"/>
+      <c r="M14" s="40"/>
     </row>
     <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
-      <c r="B15" s="53">
+      <c r="B15" s="52">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="G15" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="H15" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="I15" s="39" t="s">
-        <v>212</v>
-      </c>
-      <c r="J15" s="58" t="s">
-        <v>190</v>
-      </c>
-      <c r="K15" s="39">
+      <c r="D15" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="I15" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="J15" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="K15" s="38">
         <v>1</v>
       </c>
-      <c r="L15" s="39">
+      <c r="L15" s="38">
         <v>10</v>
       </c>
-      <c r="M15" s="42"/>
+      <c r="M15" s="41"/>
     </row>
     <row r="16" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
-      <c r="B16" s="53">
+      <c r="B16" s="52">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="37" t="s">
-        <v>21</v>
+      <c r="D16" s="69" t="s">
+        <v>20</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="G16" s="38" t="s">
-        <v>132</v>
-      </c>
-      <c r="H16" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I16" s="39" t="s">
-        <v>213</v>
-      </c>
-      <c r="J16" s="58" t="s">
-        <v>191</v>
-      </c>
-      <c r="K16" s="59">
+        <v>60</v>
+      </c>
+      <c r="F16" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I16" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="J16" s="57" t="s">
+        <v>187</v>
+      </c>
+      <c r="K16" s="58">
         <v>6</v>
       </c>
-      <c r="L16" s="39">
+      <c r="L16" s="38">
         <v>100</v>
       </c>
-      <c r="M16" s="41"/>
+      <c r="M16" s="40"/>
     </row>
     <row r="17" spans="1:13" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
-      <c r="B17" s="53">
-        <f t="shared" si="0"/>
+      <c r="B17" s="52">
+        <f>ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="F17" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="H17" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="I17" s="39" t="s">
-        <v>173</v>
-      </c>
-      <c r="J17" s="58" t="s">
-        <v>189</v>
-      </c>
-      <c r="K17" s="39">
+      <c r="D17" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I17" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="J17" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="K17" s="38">
         <v>48</v>
       </c>
-      <c r="L17" s="39">
+      <c r="L17" s="38">
         <v>300</v>
       </c>
-      <c r="M17" s="42"/>
+      <c r="M17" s="41"/>
     </row>
     <row r="18" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
-      <c r="B18" s="53">
+      <c r="B18" s="52">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>64</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>97</v>
+      <c r="D18" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>95</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>134</v>
-      </c>
-      <c r="H18" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="I18" s="39" t="s">
-        <v>174</v>
-      </c>
-      <c r="J18" s="58" t="s">
-        <v>192</v>
-      </c>
-      <c r="K18" s="39">
+        <v>237</v>
+      </c>
+      <c r="H18" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="J18" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="K18" s="38">
         <v>11</v>
       </c>
-      <c r="L18" s="39">
+      <c r="L18" s="38">
         <v>60</v>
       </c>
-      <c r="M18" s="41"/>
+      <c r="M18" s="40"/>
     </row>
     <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
-      <c r="B19" s="53">
-        <f t="shared" si="0"/>
+      <c r="B19" s="52">
+        <f>ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
-      <c r="C19" s="57" t="s">
+      <c r="C19" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D19" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="G19" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="H19" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="I19" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="J19" s="58" t="s">
-        <v>193</v>
-      </c>
-      <c r="K19" s="59">
+      <c r="D19" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I19" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="J19" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="K19" s="58">
         <v>4</v>
       </c>
-      <c r="L19" s="39">
+      <c r="L19" s="38">
         <v>100</v>
       </c>
-      <c r="M19" s="42"/>
+      <c r="M19" s="41"/>
     </row>
     <row r="20" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
-      <c r="B20" s="53">
-        <f>ROW(B20) - ROW($B$9)</f>
+      <c r="B20" s="52">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="57" t="s">
+      <c r="C20" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="G20" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I20" s="39" t="s">
-        <v>214</v>
-      </c>
-      <c r="J20" s="58" t="s">
-        <v>194</v>
-      </c>
-      <c r="K20" s="39">
+      <c r="D20" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="H20" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I20" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="J20" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="K20" s="38">
         <v>1</v>
       </c>
-      <c r="L20" s="39">
+      <c r="L20" s="38">
         <v>100</v>
       </c>
-      <c r="M20" s="41"/>
+      <c r="M20" s="40"/>
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
-      <c r="B21" s="53">
-        <f t="shared" si="0"/>
+      <c r="B21" s="52">
+        <f>ROW(B21) - ROW($B$9)</f>
         <v>12</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="D21" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="G21" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="H21" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="I21" s="39" t="s">
-        <v>176</v>
-      </c>
-      <c r="J21" s="58" t="s">
-        <v>195</v>
-      </c>
-      <c r="K21" s="59">
+      <c r="D21" s="69" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H21" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I21" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="J21" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="K21" s="58">
         <v>8</v>
       </c>
-      <c r="L21" s="39">
+      <c r="L21" s="38">
         <v>100</v>
       </c>
-      <c r="M21" s="42"/>
+      <c r="M21" s="41"/>
     </row>
     <row r="22" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="53">
-        <f>ROW(B22) - ROW($B$9)</f>
+      <c r="B22" s="52">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>27</v>
+      <c r="C22" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="69" t="s">
+        <v>26</v>
       </c>
       <c r="E22" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="F22" s="37" t="s">
-        <v>102</v>
-      </c>
-      <c r="G22" s="38"/>
-      <c r="H22" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="I22" s="39" t="s">
-        <v>215</v>
-      </c>
-      <c r="J22" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K22" s="59">
+        <v>66</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="I22" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="J22" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K22" s="58">
         <v>1</v>
       </c>
-      <c r="L22" s="39">
+      <c r="L22" s="38">
         <v>10</v>
       </c>
-      <c r="M22" s="41"/>
+      <c r="M22" s="40"/>
     </row>
     <row r="23" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="53">
-        <f t="shared" si="0"/>
+      <c r="B23" s="52">
+        <f>ROW(B23) - ROW($B$9)</f>
         <v>14</v>
       </c>
-      <c r="C23" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" s="39" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="H23" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="I23" s="39" t="s">
-        <v>217</v>
-      </c>
-      <c r="J23" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K23" s="39">
+      <c r="C23" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="J23" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K23" s="38">
         <v>1</v>
       </c>
-      <c r="L23" s="39">
+      <c r="L23" s="38">
         <v>10</v>
       </c>
-      <c r="M23" s="42"/>
+      <c r="M23" s="41"/>
     </row>
     <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
-      <c r="B24" s="53">
-        <f>ROW(B24) - ROW($B$9)</f>
+      <c r="B24" s="52">
         <v>15</v>
       </c>
-      <c r="C24" s="57" t="s">
+      <c r="C24" s="56" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="38" t="s">
-        <v>70</v>
+        <v>28</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>68</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="G24" s="38" t="s">
-        <v>139</v>
+        <v>102</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>136</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K24" s="37">
         <v>2</v>
       </c>
-      <c r="L24" s="39">
+      <c r="L24" s="38">
         <v>20</v>
       </c>
-      <c r="M24" s="41"/>
+      <c r="M24" s="40"/>
     </row>
     <row r="25" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="B25" s="53">
+      <c r="B25" s="52">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="57" t="s">
-        <v>204</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="39" t="s">
-        <v>105</v>
-      </c>
-      <c r="G25" s="39" t="s">
-        <v>232</v>
-      </c>
-      <c r="H25" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="I25" s="39" t="s">
-        <v>218</v>
-      </c>
-      <c r="J25" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K25" s="59">
+      <c r="C25" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="D25" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="H25" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="I25" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="J25" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K25" s="58">
         <v>1</v>
       </c>
-      <c r="L25" s="39">
+      <c r="L25" s="38">
         <v>20</v>
       </c>
-      <c r="M25" s="42"/>
+      <c r="M25" s="41"/>
     </row>
     <row r="26" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="B26" s="53">
+      <c r="B26" s="52">
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="57" t="s">
+      <c r="C26" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="38" t="s">
-        <v>72</v>
-      </c>
-      <c r="F26" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="G26" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="H26" s="37" t="s">
-        <v>160</v>
-      </c>
-      <c r="I26" s="39" t="s">
-        <v>178</v>
-      </c>
-      <c r="J26" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K26" s="39">
+      <c r="D26" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G26" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="H26" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="I26" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="J26" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K26" s="38">
         <v>1</v>
       </c>
-      <c r="L26" s="39">
+      <c r="L26" s="38">
         <v>10</v>
       </c>
-      <c r="M26" s="41"/>
+      <c r="M26" s="40"/>
     </row>
     <row r="27" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="B27" s="53">
+      <c r="B27" s="52">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="57" t="s">
+      <c r="C27" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="39" t="s">
-        <v>32</v>
-      </c>
-      <c r="E27" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>234</v>
-      </c>
-      <c r="G27" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="H27" s="39" t="s">
-        <v>161</v>
-      </c>
-      <c r="I27" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="J27" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K27" s="59">
+      <c r="D27" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="I27" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="J27" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K27" s="58">
         <v>8</v>
       </c>
-      <c r="L27" s="39">
+      <c r="L27" s="38">
         <v>45</v>
       </c>
-      <c r="M27" s="42"/>
+      <c r="M27" s="41"/>
     </row>
     <row r="28" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="B28" s="53">
+      <c r="B28" s="52">
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="57" t="s">
+      <c r="C28" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="38" t="s">
-        <v>74</v>
-      </c>
-      <c r="F28" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="G28" s="38" t="s">
-        <v>108</v>
-      </c>
-      <c r="H28" s="37" t="s">
-        <v>161</v>
-      </c>
-      <c r="I28" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="J28" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K28" s="39">
+      <c r="D28" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="H28" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="I28" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="J28" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="38">
         <v>4</v>
       </c>
-      <c r="L28" s="39">
+      <c r="L28" s="38">
         <v>25</v>
       </c>
-      <c r="M28" s="41"/>
+      <c r="M28" s="40"/>
     </row>
     <row r="29" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="B29" s="53">
+      <c r="B29" s="52">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="57" t="s">
-        <v>204</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="E29" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="G29" s="39" t="s">
-        <v>233</v>
-      </c>
-      <c r="H29" s="39" t="s">
-        <v>162</v>
-      </c>
-      <c r="I29" s="39" t="s">
-        <v>219</v>
-      </c>
-      <c r="J29" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K29" s="59">
+      <c r="C29" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="H29" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="I29" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="J29" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K29" s="58">
         <v>1</v>
       </c>
-      <c r="L29" s="39">
+      <c r="L29" s="38">
         <v>20</v>
       </c>
-      <c r="M29" s="42"/>
+      <c r="M29" s="41"/>
     </row>
     <row r="30" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="B30" s="53">
+      <c r="B30" s="52">
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="63" t="s">
-        <v>205</v>
-      </c>
-      <c r="D30" s="64" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="65" t="s">
-        <v>76</v>
-      </c>
-      <c r="F30" s="64" t="s">
-        <v>110</v>
-      </c>
-      <c r="G30" s="65" t="s">
-        <v>216</v>
-      </c>
-      <c r="H30" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="I30" s="60" t="s">
-        <v>216</v>
-      </c>
-      <c r="J30" s="61" t="s">
-        <v>216</v>
-      </c>
-      <c r="K30" s="60">
+      <c r="C30" s="56" t="s">
+        <v>201</v>
+      </c>
+      <c r="D30" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="59" t="s">
+        <v>230</v>
+      </c>
+      <c r="G30" s="70" t="s">
+        <v>108</v>
+      </c>
+      <c r="H30" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="I30" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="J30" s="60" t="s">
+        <v>212</v>
+      </c>
+      <c r="K30" s="59">
         <v>5</v>
       </c>
-      <c r="L30" s="60" t="s">
-        <v>216</v>
-      </c>
-      <c r="M30" s="66"/>
+      <c r="L30" s="59"/>
+      <c r="M30" s="63"/>
     </row>
     <row r="31" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="B31" s="53">
+      <c r="B31" s="52">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="57" t="s">
+      <c r="C31" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D31" s="39" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>236</v>
-      </c>
-      <c r="H31" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="I31" s="39" t="s">
-        <v>220</v>
-      </c>
-      <c r="J31" s="58" t="s">
-        <v>196</v>
-      </c>
-      <c r="K31" s="59">
+      <c r="D31" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="H31" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="I31" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="J31" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="K31" s="58">
         <v>3</v>
       </c>
-      <c r="L31" s="39">
+      <c r="L31" s="38">
         <v>100</v>
       </c>
-      <c r="M31" s="42"/>
+      <c r="M31" s="41"/>
     </row>
     <row r="32" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
-      <c r="B32" s="53">
+      <c r="B32" s="52">
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="57" t="s">
+      <c r="C32" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E32" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="F32" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="G32" s="38" t="s">
-        <v>140</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I32" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="J32" s="58" t="s">
-        <v>197</v>
-      </c>
-      <c r="K32" s="39">
+      <c r="D32" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="H32" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I32" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="K32" s="38">
         <v>8</v>
       </c>
-      <c r="L32" s="39">
+      <c r="L32" s="38">
         <v>100</v>
       </c>
-      <c r="M32" s="41"/>
+      <c r="M32" s="40"/>
     </row>
     <row r="33" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
-      <c r="B33" s="53">
+      <c r="B33" s="52">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="57" t="s">
+      <c r="C33" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="E33" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="F33" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="G33" s="40" t="s">
-        <v>141</v>
-      </c>
-      <c r="H33" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="I33" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="J33" s="58" t="s">
-        <v>198</v>
-      </c>
-      <c r="K33" s="59">
+      <c r="D33" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G33" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="H33" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="J33" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="K33" s="58">
         <v>3</v>
       </c>
-      <c r="L33" s="39">
+      <c r="L33" s="38">
         <v>100</v>
       </c>
-      <c r="M33" s="42"/>
+      <c r="M33" s="41"/>
     </row>
     <row r="34" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
-      <c r="B34" s="53">
+      <c r="B34" s="52">
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="57" t="s">
+      <c r="C34" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D34" s="37" t="s">
-        <v>39</v>
-      </c>
-      <c r="E34" s="38" t="s">
-        <v>80</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="G34" s="38" t="s">
-        <v>142</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I34" s="39" t="s">
-        <v>180</v>
-      </c>
-      <c r="J34" s="58" t="s">
-        <v>199</v>
-      </c>
-      <c r="K34" s="39">
+      <c r="D34" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="H34" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I34" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="K34" s="38">
         <v>10</v>
       </c>
-      <c r="L34" s="39">
+      <c r="L34" s="38">
         <v>100</v>
       </c>
-      <c r="M34" s="41"/>
+      <c r="M34" s="40"/>
     </row>
     <row r="35" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
-      <c r="B35" s="53">
+      <c r="B35" s="52">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="57" t="s">
+      <c r="C35" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D35" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="E35" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="F35" s="39" t="s">
-        <v>111</v>
-      </c>
-      <c r="G35" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="H35" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="I35" s="39" t="s">
-        <v>222</v>
-      </c>
-      <c r="J35" s="58" t="s">
-        <v>200</v>
-      </c>
-      <c r="K35" s="59">
+      <c r="D35" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H35" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I35" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="J35" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="K35" s="58">
         <v>2</v>
       </c>
-      <c r="L35" s="39">
+      <c r="L35" s="38">
         <v>100</v>
       </c>
-      <c r="M35" s="42"/>
+      <c r="M35" s="41"/>
     </row>
     <row r="36" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
-      <c r="B36" s="53">
+      <c r="B36" s="52">
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="57" t="s">
+      <c r="C36" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D36" s="37" t="s">
-        <v>41</v>
-      </c>
-      <c r="E36" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="F36" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="G36" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>152</v>
-      </c>
-      <c r="I36" s="39" t="s">
-        <v>181</v>
-      </c>
-      <c r="J36" s="58" t="s">
-        <v>201</v>
-      </c>
-      <c r="K36" s="39">
+      <c r="D36" s="68" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="G36" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="H36" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I36" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="J36" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="K36" s="38">
         <v>17</v>
       </c>
-      <c r="L36" s="39">
+      <c r="L36" s="38">
         <v>100</v>
       </c>
-      <c r="M36" s="41"/>
+      <c r="M36" s="40"/>
     </row>
     <row r="37" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
-      <c r="B37" s="53">
-        <f t="shared" si="0"/>
+      <c r="B37" s="52">
+        <f>ROW(B37) - ROW($B$9)</f>
         <v>28</v>
       </c>
-      <c r="C37" s="57" t="s">
+      <c r="C37" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="D37" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="E37" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="F37" s="39" t="s">
-        <v>112</v>
-      </c>
-      <c r="G37" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="H37" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="I37" s="39" t="s">
-        <v>182</v>
-      </c>
-      <c r="J37" s="58" t="s">
-        <v>202</v>
-      </c>
-      <c r="K37" s="59">
+      <c r="D37" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="H37" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I37" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="J37" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="K37" s="58">
         <v>4</v>
       </c>
-      <c r="L37" s="39">
+      <c r="L37" s="38">
         <v>100</v>
       </c>
-      <c r="M37" s="42"/>
+      <c r="M37" s="41"/>
     </row>
     <row r="38" spans="1:13" ht="180.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
-      <c r="B38" s="53">
-        <f>ROW(B38) - ROW($B$9)</f>
+      <c r="B38" s="52">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="C38" s="63" t="s">
-        <v>206</v>
-      </c>
-      <c r="D38" s="64" t="s">
-        <v>43</v>
-      </c>
-      <c r="E38" s="65" t="s">
-        <v>84</v>
-      </c>
-      <c r="F38" s="64" t="s">
-        <v>234</v>
-      </c>
-      <c r="G38" s="64" t="s">
-        <v>114</v>
-      </c>
-      <c r="H38" s="64" t="s">
-        <v>216</v>
-      </c>
-      <c r="I38" s="60" t="s">
-        <v>216</v>
-      </c>
-      <c r="J38" s="61" t="s">
-        <v>216</v>
-      </c>
-      <c r="K38" s="60">
+      <c r="C38" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="D38" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="59" t="s">
+        <v>230</v>
+      </c>
+      <c r="G38" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="H38" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="I38" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="J38" s="60" t="s">
+        <v>212</v>
+      </c>
+      <c r="K38" s="59">
         <v>106</v>
       </c>
-      <c r="L38" s="60"/>
-      <c r="M38" s="66"/>
+      <c r="L38" s="59"/>
+      <c r="M38" s="63"/>
     </row>
     <row r="39" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
-      <c r="B39" s="53">
-        <f t="shared" si="0"/>
+      <c r="B39" s="52">
+        <f>ROW(B39) - ROW($B$9)</f>
         <v>30</v>
       </c>
-      <c r="C39" s="57" t="s">
-        <v>207</v>
-      </c>
-      <c r="D39" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="F39" s="39" t="s">
-        <v>234</v>
+      <c r="C39" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" s="69" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="F39" s="38" t="s">
+        <v>230</v>
       </c>
       <c r="G39" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="H39" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="I39" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="J39" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K39" s="59">
+        <v>113</v>
+      </c>
+      <c r="H39" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="I39" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="J39" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K39" s="58">
         <v>1</v>
       </c>
-      <c r="L39" s="39">
+      <c r="L39" s="38">
         <v>10</v>
       </c>
-      <c r="M39" s="42"/>
+      <c r="M39" s="41"/>
     </row>
     <row r="40" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
-      <c r="B40" s="53">
-        <f>ROW(B40) - ROW($B$9)</f>
+      <c r="B40" s="52">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="C40" s="57" t="s">
+      <c r="C40" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="D40" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="G40" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="H40" s="37" t="s">
-        <v>163</v>
-      </c>
-      <c r="I40" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="J40" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K40" s="39">
+      <c r="D40" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G40" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="H40" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="I40" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="J40" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K40" s="38">
         <v>1</v>
       </c>
-      <c r="L40" s="39">
+      <c r="L40" s="38">
         <v>6</v>
       </c>
-      <c r="M40" s="41"/>
+      <c r="M40" s="40"/>
     </row>
     <row r="41" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
-      <c r="B41" s="53">
-        <f t="shared" si="0"/>
+      <c r="B41" s="52">
+        <f>ROW(B41) - ROW($B$9)</f>
         <v>32</v>
       </c>
-      <c r="C41" s="57" t="s">
+      <c r="C41" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="E41" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="F41" s="39" t="s">
-        <v>117</v>
-      </c>
-      <c r="G41" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="H41" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="I41" s="39" t="s">
-        <v>184</v>
-      </c>
-      <c r="J41" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K41" s="59">
+      <c r="D41" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="G41" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="H41" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I41" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="J41" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K41" s="58">
         <v>8</v>
       </c>
-      <c r="L41" s="39">
+      <c r="L41" s="38">
         <v>42</v>
       </c>
-      <c r="M41" s="42"/>
+      <c r="M41" s="41"/>
     </row>
     <row r="42" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
-      <c r="B42" s="53">
-        <f>ROW(B42) - ROW($B$9)</f>
+      <c r="B42" s="52">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="C42" s="57" t="s">
+      <c r="C42" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="E42" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="G42" s="38" t="s">
-        <v>147</v>
-      </c>
-      <c r="H42" s="37" t="s">
-        <v>164</v>
-      </c>
-      <c r="I42" s="39" t="s">
-        <v>224</v>
-      </c>
-      <c r="J42" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K42" s="39">
+      <c r="D42" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="G42" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="H42" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I42" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="J42" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K42" s="38">
         <v>1</v>
       </c>
-      <c r="L42" s="39">
+      <c r="L42" s="38">
         <v>6</v>
       </c>
-      <c r="M42" s="41"/>
+      <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
-      <c r="B43" s="53">
-        <f t="shared" si="0"/>
+      <c r="B43" s="52">
+        <f>ROW(B43) - ROW($B$9)</f>
         <v>34</v>
       </c>
-      <c r="C43" s="57" t="s">
+      <c r="C43" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="E43" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="F43" s="39" t="s">
-        <v>119</v>
-      </c>
-      <c r="G43" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="H43" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="I43" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="J43" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K43" s="59">
+      <c r="D43" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="G43" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="H43" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I43" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="J43" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K43" s="58">
         <v>1</v>
       </c>
-      <c r="L43" s="39">
+      <c r="L43" s="38">
         <v>6</v>
       </c>
-      <c r="M43" s="42"/>
+      <c r="M43" s="41"/>
     </row>
     <row r="44" spans="1:13" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
-      <c r="B44" s="53">
-        <f>ROW(B44) - ROW($B$9)</f>
+      <c r="B44" s="52">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="C44" s="57" t="s">
+      <c r="C44" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="D44" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="E44" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="F44" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="G44" s="38" t="s">
-        <v>120</v>
-      </c>
-      <c r="H44" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="I44" s="39" t="s">
-        <v>225</v>
-      </c>
-      <c r="J44" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K44" s="39">
+      <c r="D44" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="G44" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="H44" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I44" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="J44" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K44" s="38">
         <v>2</v>
       </c>
-      <c r="L44" s="39">
+      <c r="L44" s="38">
         <v>11</v>
       </c>
-      <c r="M44" s="41"/>
+      <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
-      <c r="B45" s="53">
-        <f t="shared" si="0"/>
+      <c r="B45" s="52">
+        <f>ROW(B45) - ROW($B$9)</f>
         <v>36</v>
       </c>
-      <c r="C45" s="57" t="s">
+      <c r="C45" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="D45" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="E45" s="40" t="s">
-        <v>91</v>
-      </c>
-      <c r="F45" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="G45" s="39" t="s">
-        <v>121</v>
-      </c>
-      <c r="H45" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="I45" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="J45" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K45" s="59">
+      <c r="D45" s="69" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="G45" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="H45" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I45" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="J45" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K45" s="58">
         <v>1</v>
       </c>
-      <c r="L45" s="39">
+      <c r="L45" s="38">
         <v>10</v>
       </c>
-      <c r="M45" s="42"/>
+      <c r="M45" s="41"/>
     </row>
     <row r="46" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
-      <c r="B46" s="53">
-        <f>ROW(B46) - ROW($B$9)</f>
+      <c r="B46" s="52">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="C46" s="57" t="s">
+      <c r="C46" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="D46" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="E46" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="F46" s="37" t="s">
-        <v>122</v>
-      </c>
-      <c r="G46" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="H46" s="37" t="s">
-        <v>157</v>
-      </c>
-      <c r="I46" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="J46" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K46" s="39">
+      <c r="D46" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="E46" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G46" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="H46" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I46" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="J46" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K46" s="38">
         <v>1</v>
       </c>
-      <c r="L46" s="39">
+      <c r="L46" s="38">
         <v>6</v>
       </c>
-      <c r="M46" s="41"/>
+      <c r="M46" s="40"/>
     </row>
     <row r="47" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
-      <c r="B47" s="53">
-        <f t="shared" si="0"/>
+      <c r="B47" s="52">
+        <f>ROW(B47) - ROW($B$9)</f>
         <v>38</v>
       </c>
-      <c r="C47" s="57" t="s">
+      <c r="C47" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="D47" s="39" t="s">
-        <v>52</v>
-      </c>
-      <c r="E47" s="40" t="s">
-        <v>93</v>
-      </c>
-      <c r="F47" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="G47" s="40" t="s">
-        <v>150</v>
-      </c>
-      <c r="H47" s="39" t="s">
-        <v>166</v>
-      </c>
-      <c r="I47" s="39" t="s">
-        <v>216</v>
-      </c>
-      <c r="J47" s="58" t="s">
-        <v>216</v>
-      </c>
-      <c r="K47" s="59">
+      <c r="D47" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="G47" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="H47" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="I47" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="J47" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K47" s="58">
         <v>4</v>
       </c>
-      <c r="L47" s="39">
+      <c r="L47" s="38">
         <v>21</v>
       </c>
-      <c r="M47" s="42"/>
+      <c r="M47" s="41"/>
     </row>
     <row r="48" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
-      <c r="B48" s="53">
-        <f>ROW(B48) - ROW($B$9)</f>
+      <c r="B48" s="52">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="C48" s="57" t="s">
-        <v>208</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="E48" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="G48" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="H48" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="I48" s="39" t="s">
-        <v>226</v>
-      </c>
-      <c r="J48" s="58" t="s">
-        <v>227</v>
-      </c>
-      <c r="K48" s="39">
+      <c r="C48" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="D48" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G48" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="H48" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="I48" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="J48" s="57" t="s">
+        <v>223</v>
+      </c>
+      <c r="K48" s="38">
         <v>1</v>
       </c>
-      <c r="L48" s="39">
+      <c r="L48" s="38">
         <v>6</v>
       </c>
-      <c r="M48" s="41"/>
+      <c r="M48" s="40"/>
     </row>
     <row r="49" spans="1:13" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
-      <c r="B49" s="53">
-        <f t="shared" si="0"/>
+      <c r="B49" s="52">
+        <f>ROW(B49) - ROW($B$9)</f>
         <v>40</v>
       </c>
-      <c r="C49" s="57" t="s">
-        <v>208</v>
-      </c>
-      <c r="D49" s="39" t="s">
-        <v>54</v>
-      </c>
-      <c r="E49" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="F49" s="39" t="s">
-        <v>234</v>
-      </c>
-      <c r="G49" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="H49" s="39" t="s">
-        <v>168</v>
-      </c>
-      <c r="I49" s="39" t="s">
-        <v>228</v>
-      </c>
-      <c r="J49" s="58" t="s">
-        <v>229</v>
-      </c>
-      <c r="K49" s="62">
+      <c r="C49" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="D49" s="69" t="s">
+        <v>52</v>
+      </c>
+      <c r="E49" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G49" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="H49" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="I49" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="J49" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="K49" s="61">
         <v>2</v>
       </c>
-      <c r="L49" s="39">
+      <c r="L49" s="38">
         <v>15</v>
       </c>
-      <c r="M49" s="42"/>
+      <c r="M49" s="41"/>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="1"/>
       <c r="B50" s="32"/>
-      <c r="C50" s="51"/>
+      <c r="C50" s="50"/>
       <c r="D50" s="33"/>
       <c r="E50" s="34"/>
       <c r="F50" s="35"/>
@@ -3459,12 +3576,12 @@
       <c r="J50" s="36"/>
       <c r="K50" s="36"/>
       <c r="L50" s="36"/>
-      <c r="M50" s="44"/>
+      <c r="M50" s="43"/>
     </row>
     <row r="51" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="24"/>
-      <c r="C51" s="52"/>
+      <c r="C51" s="51"/>
       <c r="D51" s="8"/>
       <c r="E51" s="9"/>
       <c r="F51" s="9"/>
@@ -3474,7 +3591,7 @@
       <c r="J51" s="9"/>
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
-      <c r="M51" s="45"/>
+      <c r="M51" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3485,4 +3602,1757 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M51"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="64"/>
+      <c r="M1" s="64"/>
+    </row>
+    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="53" t="s">
+        <v>234</v>
+      </c>
+      <c r="G2" s="11"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="42"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="12"/>
+      <c r="F3" s="54" t="s">
+        <v>235</v>
+      </c>
+      <c r="G3" s="12"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="65"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="12"/>
+      <c r="F4" s="54" t="s">
+        <v>235</v>
+      </c>
+      <c r="G4" s="13"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="66"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="46"/>
+      <c r="D5" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="66"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="14"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+      <c r="K6" s="5"/>
+      <c r="L6" s="5"/>
+      <c r="M6" s="66"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="66"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="26"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="66"/>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="67" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="29" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="H9" s="30" t="s">
+        <v>148</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>244</v>
+      </c>
+      <c r="M9" s="31" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="72"/>
+      <c r="B10" s="52">
+        <f>ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="68" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>54</v>
+      </c>
+      <c r="F10" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="H10" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>167</v>
+      </c>
+      <c r="J10" s="57" t="s">
+        <v>181</v>
+      </c>
+      <c r="K10" s="38">
+        <v>9</v>
+      </c>
+      <c r="L10" s="38">
+        <v>100</v>
+      </c>
+      <c r="M10" s="40"/>
+    </row>
+    <row r="11" spans="1:13" s="73" customFormat="1" ht="84.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="72"/>
+      <c r="B11" s="52">
+        <f>ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="68" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G11" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="H11" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="J11" s="57" t="s">
+        <v>182</v>
+      </c>
+      <c r="K11" s="38">
+        <v>51</v>
+      </c>
+      <c r="L11" s="38">
+        <v>550</v>
+      </c>
+      <c r="M11" s="41"/>
+    </row>
+    <row r="12" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="72"/>
+      <c r="B12" s="52">
+        <f t="shared" ref="B12:B48" si="0">ROW(B12) - ROW($B$9)</f>
+        <v>3</v>
+      </c>
+      <c r="C12" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="69" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="G12" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="H12" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="J12" s="57" t="s">
+        <v>183</v>
+      </c>
+      <c r="K12" s="58">
+        <v>12</v>
+      </c>
+      <c r="L12" s="38">
+        <v>200</v>
+      </c>
+      <c r="M12" s="40"/>
+    </row>
+    <row r="13" spans="1:13" s="83" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="74"/>
+      <c r="B13" s="75">
+        <f>ROW(B13) - ROW($B$9)</f>
+        <v>4</v>
+      </c>
+      <c r="C13" s="76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="84" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="79" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="78" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="79" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13" s="78" t="s">
+        <v>150</v>
+      </c>
+      <c r="I13" s="78" t="s">
+        <v>169</v>
+      </c>
+      <c r="J13" s="80" t="s">
+        <v>184</v>
+      </c>
+      <c r="K13" s="78">
+        <v>2</v>
+      </c>
+      <c r="L13" s="78">
+        <v>21</v>
+      </c>
+      <c r="M13" s="85"/>
+    </row>
+    <row r="14" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="72"/>
+      <c r="B14" s="52">
+        <f>ROW(B14) - ROW($B$9)</f>
+        <v>5</v>
+      </c>
+      <c r="C14" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D14" s="69" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G14" s="38" t="s">
+        <v>227</v>
+      </c>
+      <c r="H14" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="J14" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="K14" s="58">
+        <v>16</v>
+      </c>
+      <c r="L14" s="38">
+        <v>200</v>
+      </c>
+      <c r="M14" s="40"/>
+    </row>
+    <row r="15" spans="1:13" s="73" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="72"/>
+      <c r="B15" s="52">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C15" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D15" s="68" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G15" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="H15" s="38" t="s">
+        <v>151</v>
+      </c>
+      <c r="I15" s="38" t="s">
+        <v>208</v>
+      </c>
+      <c r="J15" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="K15" s="38">
+        <v>1</v>
+      </c>
+      <c r="L15" s="38">
+        <v>20</v>
+      </c>
+      <c r="M15" s="41"/>
+    </row>
+    <row r="16" spans="1:13" s="83" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="74"/>
+      <c r="B16" s="75">
+        <f>ROW(B16) - ROW($B$9)</f>
+        <v>7</v>
+      </c>
+      <c r="C16" s="76" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="77" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="78" t="s">
+        <v>60</v>
+      </c>
+      <c r="F16" s="78" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="79" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="78" t="s">
+        <v>149</v>
+      </c>
+      <c r="I16" s="78" t="s">
+        <v>209</v>
+      </c>
+      <c r="J16" s="80" t="s">
+        <v>187</v>
+      </c>
+      <c r="K16" s="81">
+        <v>6</v>
+      </c>
+      <c r="L16" s="78">
+        <v>100</v>
+      </c>
+      <c r="M16" s="82"/>
+    </row>
+    <row r="17" spans="1:13" s="73" customFormat="1" ht="96.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="72"/>
+      <c r="B17" s="52">
+        <f>ROW(B17) - ROW($B$9)</f>
+        <v>8</v>
+      </c>
+      <c r="C17" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="68" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>131</v>
+      </c>
+      <c r="H17" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I17" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="J17" s="57" t="s">
+        <v>185</v>
+      </c>
+      <c r="K17" s="38">
+        <v>48</v>
+      </c>
+      <c r="L17" s="38">
+        <v>500</v>
+      </c>
+      <c r="M17" s="41"/>
+    </row>
+    <row r="18" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="72"/>
+      <c r="B18" s="52">
+        <f>ROW(B18) - ROW($B$9)</f>
+        <v>9</v>
+      </c>
+      <c r="C18" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D18" s="69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G18" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="H18" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="I18" s="38" t="s">
+        <v>241</v>
+      </c>
+      <c r="J18" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="K18" s="38">
+        <v>11</v>
+      </c>
+      <c r="L18" s="38">
+        <v>120</v>
+      </c>
+      <c r="M18" s="40"/>
+    </row>
+    <row r="19" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="72"/>
+      <c r="B19" s="52">
+        <f>ROW(B19) - ROW($B$9)</f>
+        <v>10</v>
+      </c>
+      <c r="C19" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>63</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="H19" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I19" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="J19" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="K19" s="58">
+        <v>4</v>
+      </c>
+      <c r="L19" s="38">
+        <v>100</v>
+      </c>
+      <c r="M19" s="41"/>
+    </row>
+    <row r="20" spans="1:13" s="73" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="72"/>
+      <c r="B20" s="52">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C20" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="F20" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="G20" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="H20" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I20" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="J20" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="K20" s="38">
+        <v>1</v>
+      </c>
+      <c r="L20" s="38">
+        <v>100</v>
+      </c>
+      <c r="M20" s="40"/>
+    </row>
+    <row r="21" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="72"/>
+      <c r="B21" s="52">
+        <f>ROW(B21) - ROW($B$9)</f>
+        <v>12</v>
+      </c>
+      <c r="C21" s="56" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21" s="69" t="s">
+        <v>25</v>
+      </c>
+      <c r="E21" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H21" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I21" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="J21" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="K21" s="58">
+        <v>8</v>
+      </c>
+      <c r="L21" s="38">
+        <v>100</v>
+      </c>
+      <c r="M21" s="41"/>
+    </row>
+    <row r="22" spans="1:13" s="73" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="72"/>
+      <c r="B22" s="52">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C22" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="D22" s="69" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="F22" s="38" t="s">
+        <v>238</v>
+      </c>
+      <c r="G22" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="H22" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="I22" s="38" t="s">
+        <v>211</v>
+      </c>
+      <c r="J22" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K22" s="58">
+        <v>1</v>
+      </c>
+      <c r="L22" s="38">
+        <v>20</v>
+      </c>
+      <c r="M22" s="40"/>
+    </row>
+    <row r="23" spans="1:13" s="73" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="72"/>
+      <c r="B23" s="52">
+        <f>ROW(B23) - ROW($B$9)</f>
+        <v>14</v>
+      </c>
+      <c r="C23" s="56" t="s">
+        <v>199</v>
+      </c>
+      <c r="D23" s="68" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="F23" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="H23" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="J23" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K23" s="38">
+        <v>1</v>
+      </c>
+      <c r="L23" s="38">
+        <v>20</v>
+      </c>
+      <c r="M23" s="41"/>
+    </row>
+    <row r="24" spans="1:13" s="73" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="72"/>
+      <c r="B24" s="52">
+        <v>15</v>
+      </c>
+      <c r="C24" s="56" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>136</v>
+      </c>
+      <c r="H24" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="I24" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="J24" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="K24" s="37">
+        <v>2</v>
+      </c>
+      <c r="L24" s="38">
+        <v>40</v>
+      </c>
+      <c r="M24" s="40"/>
+    </row>
+    <row r="25" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="72"/>
+      <c r="B25" s="52">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C25" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="D25" s="69" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="F25" s="38" t="s">
+        <v>103</v>
+      </c>
+      <c r="G25" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="H25" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="I25" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="J25" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K25" s="58">
+        <v>1</v>
+      </c>
+      <c r="L25" s="38">
+        <v>20</v>
+      </c>
+      <c r="M25" s="41"/>
+    </row>
+    <row r="26" spans="1:13" s="73" customFormat="1" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="72"/>
+      <c r="B26" s="52">
+        <f>ROW(B26) - ROW($B$9)</f>
+        <v>17</v>
+      </c>
+      <c r="C26" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="68" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G26" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="H26" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="I26" s="38" t="s">
+        <v>174</v>
+      </c>
+      <c r="J26" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K26" s="38">
+        <v>1</v>
+      </c>
+      <c r="L26" s="38">
+        <v>20</v>
+      </c>
+      <c r="M26" s="40"/>
+    </row>
+    <row r="27" spans="1:13" s="73" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="72"/>
+      <c r="B27" s="52">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C27" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="69" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>71</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="I27" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="J27" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K27" s="58">
+        <v>8</v>
+      </c>
+      <c r="L27" s="38">
+        <v>85</v>
+      </c>
+      <c r="M27" s="41"/>
+    </row>
+    <row r="28" spans="1:13" s="73" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="72"/>
+      <c r="B28" s="52">
+        <f>ROW(B28) - ROW($B$9)</f>
+        <v>19</v>
+      </c>
+      <c r="C28" s="56" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="68" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>106</v>
+      </c>
+      <c r="H28" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="I28" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="J28" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K28" s="38">
+        <v>4</v>
+      </c>
+      <c r="L28" s="38">
+        <v>45</v>
+      </c>
+      <c r="M28" s="40"/>
+    </row>
+    <row r="29" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="72"/>
+      <c r="B29" s="52">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C29" s="56" t="s">
+        <v>200</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>33</v>
+      </c>
+      <c r="E29" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F29" s="38" t="s">
+        <v>107</v>
+      </c>
+      <c r="G29" s="38" t="s">
+        <v>229</v>
+      </c>
+      <c r="H29" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="I29" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="J29" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K29" s="58">
+        <v>1</v>
+      </c>
+      <c r="L29" s="38">
+        <v>20</v>
+      </c>
+      <c r="M29" s="41"/>
+    </row>
+    <row r="30" spans="1:13" s="73" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="72"/>
+      <c r="B30" s="52">
+        <f>ROW(B30) - ROW($B$9)</f>
+        <v>21</v>
+      </c>
+      <c r="C30" s="56" t="s">
+        <v>201</v>
+      </c>
+      <c r="D30" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="E30" s="70" t="s">
+        <v>74</v>
+      </c>
+      <c r="F30" s="59" t="s">
+        <v>230</v>
+      </c>
+      <c r="G30" s="70" t="s">
+        <v>108</v>
+      </c>
+      <c r="H30" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="I30" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="J30" s="60" t="s">
+        <v>212</v>
+      </c>
+      <c r="K30" s="59">
+        <v>5</v>
+      </c>
+      <c r="L30" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="M30" s="63"/>
+    </row>
+    <row r="31" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="72"/>
+      <c r="B31" s="52">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C31" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="69" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="F31" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>232</v>
+      </c>
+      <c r="H31" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="I31" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="J31" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="K31" s="58">
+        <v>3</v>
+      </c>
+      <c r="L31" s="38">
+        <v>100</v>
+      </c>
+      <c r="M31" s="41"/>
+    </row>
+    <row r="32" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="72"/>
+      <c r="B32" s="52">
+        <f>ROW(B32) - ROW($B$9)</f>
+        <v>23</v>
+      </c>
+      <c r="C32" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="68" t="s">
+        <v>36</v>
+      </c>
+      <c r="E32" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="F32" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="H32" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I32" s="38" t="s">
+        <v>175</v>
+      </c>
+      <c r="J32" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="K32" s="38">
+        <v>8</v>
+      </c>
+      <c r="L32" s="38">
+        <v>100</v>
+      </c>
+      <c r="M32" s="40"/>
+    </row>
+    <row r="33" spans="1:13" s="73" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="72"/>
+      <c r="B33" s="52">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C33" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="69" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G33" s="39" t="s">
+        <v>138</v>
+      </c>
+      <c r="H33" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I33" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="J33" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="K33" s="58">
+        <v>3</v>
+      </c>
+      <c r="L33" s="38">
+        <v>100</v>
+      </c>
+      <c r="M33" s="41"/>
+    </row>
+    <row r="34" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="72"/>
+      <c r="B34" s="52">
+        <f>ROW(B34) - ROW($B$9)</f>
+        <v>25</v>
+      </c>
+      <c r="C34" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="E34" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>139</v>
+      </c>
+      <c r="H34" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I34" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="J34" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="K34" s="38">
+        <v>10</v>
+      </c>
+      <c r="L34" s="38">
+        <v>200</v>
+      </c>
+      <c r="M34" s="40"/>
+    </row>
+    <row r="35" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="72"/>
+      <c r="B35" s="52">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="C35" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="69" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="G35" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H35" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I35" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="J35" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="K35" s="58">
+        <v>2</v>
+      </c>
+      <c r="L35" s="38">
+        <v>100</v>
+      </c>
+      <c r="M35" s="41"/>
+    </row>
+    <row r="36" spans="1:13" s="73" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="72"/>
+      <c r="B36" s="52">
+        <f>ROW(B36) - ROW($B$9)</f>
+        <v>27</v>
+      </c>
+      <c r="C36" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="68" t="s">
+        <v>239</v>
+      </c>
+      <c r="E36" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="F36" s="38" t="s">
+        <v>111</v>
+      </c>
+      <c r="G36" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="H36" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I36" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="J36" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="K36" s="38">
+        <v>17</v>
+      </c>
+      <c r="L36" s="38">
+        <v>200</v>
+      </c>
+      <c r="M36" s="40"/>
+    </row>
+    <row r="37" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="72"/>
+      <c r="B37" s="52">
+        <f>ROW(B37) - ROW($B$9)</f>
+        <v>28</v>
+      </c>
+      <c r="C37" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="69" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G37" s="39" t="s">
+        <v>142</v>
+      </c>
+      <c r="H37" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="I37" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="J37" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="K37" s="58">
+        <v>4</v>
+      </c>
+      <c r="L37" s="38">
+        <v>100</v>
+      </c>
+      <c r="M37" s="41"/>
+    </row>
+    <row r="38" spans="1:13" s="73" customFormat="1" ht="216.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="72"/>
+      <c r="B38" s="52">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="C38" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="D38" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="70" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="59" t="s">
+        <v>230</v>
+      </c>
+      <c r="G38" s="70" t="s">
+        <v>112</v>
+      </c>
+      <c r="H38" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="I38" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="J38" s="60" t="s">
+        <v>212</v>
+      </c>
+      <c r="K38" s="59">
+        <v>106</v>
+      </c>
+      <c r="L38" s="59" t="s">
+        <v>212</v>
+      </c>
+      <c r="M38" s="63"/>
+    </row>
+    <row r="39" spans="1:13" s="73" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="72"/>
+      <c r="B39" s="52">
+        <f>ROW(B39) - ROW($B$9)</f>
+        <v>30</v>
+      </c>
+      <c r="C39" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="D39" s="69" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="F39" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G39" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="H39" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="I39" s="38" t="s">
+        <v>219</v>
+      </c>
+      <c r="J39" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K39" s="58">
+        <v>1</v>
+      </c>
+      <c r="L39" s="38">
+        <v>20</v>
+      </c>
+      <c r="M39" s="41"/>
+    </row>
+    <row r="40" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="72"/>
+      <c r="B40" s="52">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="C40" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="68" t="s">
+        <v>43</v>
+      </c>
+      <c r="E40" s="39" t="s">
+        <v>84</v>
+      </c>
+      <c r="F40" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G40" s="39" t="s">
+        <v>114</v>
+      </c>
+      <c r="H40" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="I40" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="J40" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K40" s="38">
+        <v>1</v>
+      </c>
+      <c r="L40" s="38">
+        <v>11</v>
+      </c>
+      <c r="M40" s="40"/>
+    </row>
+    <row r="41" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="72"/>
+      <c r="B41" s="52">
+        <f>ROW(B41) - ROW($B$9)</f>
+        <v>32</v>
+      </c>
+      <c r="C41" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" s="69" t="s">
+        <v>44</v>
+      </c>
+      <c r="E41" s="38" t="s">
+        <v>85</v>
+      </c>
+      <c r="F41" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="G41" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="H41" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I41" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="J41" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K41" s="58">
+        <v>8</v>
+      </c>
+      <c r="L41" s="38">
+        <v>81</v>
+      </c>
+      <c r="M41" s="41"/>
+    </row>
+    <row r="42" spans="1:13" s="73" customFormat="1" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="72"/>
+      <c r="B42" s="52">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="C42" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="F42" s="38" t="s">
+        <v>116</v>
+      </c>
+      <c r="G42" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="H42" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="I42" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="J42" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K42" s="38">
+        <v>1</v>
+      </c>
+      <c r="L42" s="38">
+        <v>11</v>
+      </c>
+      <c r="M42" s="40"/>
+    </row>
+    <row r="43" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="72"/>
+      <c r="B43" s="52">
+        <f>ROW(B43) - ROW($B$9)</f>
+        <v>34</v>
+      </c>
+      <c r="C43" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="E43" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="F43" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="G43" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="H43" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I43" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="J43" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K43" s="58">
+        <v>1</v>
+      </c>
+      <c r="L43" s="38">
+        <v>11</v>
+      </c>
+      <c r="M43" s="41"/>
+    </row>
+    <row r="44" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="72"/>
+      <c r="B44" s="52">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="C44" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" s="68" t="s">
+        <v>47</v>
+      </c>
+      <c r="E44" s="39" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" s="38" t="s">
+        <v>240</v>
+      </c>
+      <c r="G44" s="39" t="s">
+        <v>118</v>
+      </c>
+      <c r="H44" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I44" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="J44" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K44" s="38">
+        <v>2</v>
+      </c>
+      <c r="L44" s="38">
+        <v>21</v>
+      </c>
+      <c r="M44" s="40"/>
+    </row>
+    <row r="45" spans="1:13" s="73" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="72"/>
+      <c r="B45" s="52">
+        <f>ROW(B45) - ROW($B$9)</f>
+        <v>36</v>
+      </c>
+      <c r="C45" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" s="69" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>231</v>
+      </c>
+      <c r="G45" s="71" t="s">
+        <v>119</v>
+      </c>
+      <c r="H45" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="I45" s="38" t="s">
+        <v>242</v>
+      </c>
+      <c r="J45" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K45" s="58">
+        <v>1</v>
+      </c>
+      <c r="L45" s="38">
+        <v>20</v>
+      </c>
+      <c r="M45" s="41"/>
+    </row>
+    <row r="46" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="72"/>
+      <c r="B46" s="52">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="C46" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" s="68" t="s">
+        <v>49</v>
+      </c>
+      <c r="E46" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="F46" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="G46" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="H46" s="38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I46" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="J46" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K46" s="38">
+        <v>1</v>
+      </c>
+      <c r="L46" s="38">
+        <v>11</v>
+      </c>
+      <c r="M46" s="40"/>
+    </row>
+    <row r="47" spans="1:13" s="73" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="72"/>
+      <c r="B47" s="52">
+        <f>ROW(B47) - ROW($B$9)</f>
+        <v>38</v>
+      </c>
+      <c r="C47" s="56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>121</v>
+      </c>
+      <c r="G47" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="H47" s="38" t="s">
+        <v>163</v>
+      </c>
+      <c r="I47" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="J47" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="K47" s="58">
+        <v>4</v>
+      </c>
+      <c r="L47" s="38">
+        <v>41</v>
+      </c>
+      <c r="M47" s="41"/>
+    </row>
+    <row r="48" spans="1:13" s="73" customFormat="1" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="72"/>
+      <c r="B48" s="52">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="C48" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="D48" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="F48" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G48" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="H48" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="I48" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="J48" s="57" t="s">
+        <v>223</v>
+      </c>
+      <c r="K48" s="38">
+        <v>1</v>
+      </c>
+      <c r="L48" s="38">
+        <v>15</v>
+      </c>
+      <c r="M48" s="40"/>
+    </row>
+    <row r="49" spans="1:13" s="73" customFormat="1" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="72"/>
+      <c r="B49" s="52">
+        <f>ROW(B49) - ROW($B$9)</f>
+        <v>40</v>
+      </c>
+      <c r="C49" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="D49" s="69" t="s">
+        <v>52</v>
+      </c>
+      <c r="E49" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>230</v>
+      </c>
+      <c r="G49" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="H49" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="I49" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="J49" s="57" t="s">
+        <v>225</v>
+      </c>
+      <c r="K49" s="61">
+        <v>2</v>
+      </c>
+      <c r="L49" s="38">
+        <v>25</v>
+      </c>
+      <c r="M49" s="41"/>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" s="1"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="50"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="34"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="36"/>
+      <c r="M50" s="43"/>
+    </row>
+    <row r="51" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1"/>
+      <c r="B51" s="24"/>
+      <c r="C51" s="51"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+      <c r="M51" s="44"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="M3:M8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>